--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -70,142 +70,10 @@
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>CANTE</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>TOMAS RAFAEL</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>CELINA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>JOSE MARCELO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ULISES HIRAM</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -606,16 +474,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -671,7 +542,7 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -730,16 +601,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +623,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -787,10 +661,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -799,394 +673,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920293</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920295</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920360</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920415</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920300</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920301</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920304</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920305</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920306</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920307</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920310</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920311</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920313</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920370</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920314</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920315</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
@@ -673,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
@@ -673,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
@@ -539,16 +539,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -604,16 +607,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>93.94</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -607,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>90.91</v>
+        <v>93.94</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -656,29 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
